--- a/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2017_T2_0.xlsx
+++ b/data/controles_results/dif_medias/dep_vars/ddifmedias_dep_vars_2017_T2_0.xlsx
@@ -57,7 +57,7 @@
     <t>N</t>
   </si>
   <si>
-    <t>91</t>
+    <t>87</t>
   </si>
   <si>
     <t xml:space="preserve"> (1) </t>
@@ -69,64 +69,64 @@
     <t>Mean/(SE)</t>
   </si>
   <si>
-    <t>1.316</t>
-  </si>
-  <si>
-    <t>(0.231)</t>
-  </si>
-  <si>
-    <t>7.330</t>
-  </si>
-  <si>
-    <t>(0.855)</t>
-  </si>
-  <si>
-    <t>43.654</t>
-  </si>
-  <si>
-    <t>(9.738)</t>
-  </si>
-  <si>
-    <t>52.327</t>
-  </si>
-  <si>
-    <t>(11.839)</t>
-  </si>
-  <si>
-    <t>1.292</t>
-  </si>
-  <si>
-    <t>(0.201)</t>
-  </si>
-  <si>
-    <t>6.978</t>
-  </si>
-  <si>
-    <t>(0.759)</t>
-  </si>
-  <si>
-    <t>2.414</t>
-  </si>
-  <si>
-    <t>(0.569)</t>
-  </si>
-  <si>
-    <t>3.651</t>
-  </si>
-  <si>
-    <t>(2.391)</t>
-  </si>
-  <si>
-    <t>55.315</t>
-  </si>
-  <si>
-    <t>(9.576)</t>
-  </si>
-  <si>
-    <t>50.916</t>
-  </si>
-  <si>
-    <t>(16.780)</t>
+    <t>1.377</t>
+  </si>
+  <si>
+    <t>(0.240)</t>
+  </si>
+  <si>
+    <t>7.667</t>
+  </si>
+  <si>
+    <t>(0.878)</t>
+  </si>
+  <si>
+    <t>33.942</t>
+  </si>
+  <si>
+    <t>(6.581)</t>
+  </si>
+  <si>
+    <t>40.112</t>
+  </si>
+  <si>
+    <t>(7.419)</t>
+  </si>
+  <si>
+    <t>1.352</t>
+  </si>
+  <si>
+    <t>(0.208)</t>
+  </si>
+  <si>
+    <t>7.299</t>
+  </si>
+  <si>
+    <t>(0.776)</t>
+  </si>
+  <si>
+    <t>2.499</t>
+  </si>
+  <si>
+    <t>(0.593)</t>
+  </si>
+  <si>
+    <t>0.942</t>
+  </si>
+  <si>
+    <t>(0.427)</t>
+  </si>
+  <si>
+    <t>47.367</t>
+  </si>
+  <si>
+    <t>(8.181)</t>
+  </si>
+  <si>
+    <t>34.017</t>
+  </si>
+  <si>
+    <t>(6.946)</t>
   </si>
   <si>
     <t>23</t>
@@ -198,7 +198,7 @@
     <t>(20.254)</t>
   </si>
   <si>
-    <t>114</t>
+    <t>110</t>
   </si>
   <si>
     <t>(2)-(1)</t>
@@ -210,34 +210,34 @@
     <t>Mean difference</t>
   </si>
   <si>
-    <t>1.108*</t>
-  </si>
-  <si>
-    <t>0.323</t>
-  </si>
-  <si>
-    <t>42.802*</t>
-  </si>
-  <si>
-    <t>42.472</t>
-  </si>
-  <si>
-    <t>1.159**</t>
-  </si>
-  <si>
-    <t>2.109</t>
-  </si>
-  <si>
-    <t>0.639</t>
-  </si>
-  <si>
-    <t>-3.237</t>
-  </si>
-  <si>
-    <t>62.042**</t>
-  </si>
-  <si>
-    <t>23.159</t>
+    <t>1.047</t>
+  </si>
+  <si>
+    <t>-0.014</t>
+  </si>
+  <si>
+    <t>52.514***</t>
+  </si>
+  <si>
+    <t>54.687***</t>
+  </si>
+  <si>
+    <t>1.100*</t>
+  </si>
+  <si>
+    <t>1.788</t>
+  </si>
+  <si>
+    <t>0.554</t>
+  </si>
+  <si>
+    <t>-0.528</t>
+  </si>
+  <si>
+    <t>69.990***</t>
+  </si>
+  <si>
+    <t>40.058**</t>
   </si>
 </sst>
 </file>
